--- a/Excel/new_jobs(post).xlsx
+++ b/Excel/new_jobs(post).xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>post_date</t>
+          <t>post_date_str</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1783105749379</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/Excel/new_jobs(post).xlsx
+++ b/Excel/new_jobs(post).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,45 +466,50 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>post_date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>is_remote</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>is_hybrid</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TZ</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>is_US</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
@@ -548,37 +553,42 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>New York, NY, United States of America</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5114747008?gh_jid=5114747008</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Block is one company built from many blocks, all united by the same purpose of economic empowerment. The blocks that form our foundational teams — People, Finance, Counsel, Hardware, Information Security, Platform Infrastructure Engineering, and more — provide support and guidance at the corporate level. They work across business groups and around the globe, spanning time zones and disciplines to develop inclusive People policies, forecast finances, give legal counsel, safeguard systems, nurture new initiatives, and more. Every challenge creates possibilities, and we need different perspectives to see them all. Bring yours to Block. The Role The Staff Data Analyst will join the Block Compliance Analytics team chartered to put data at the center of the Compliance organization. You have a proven track record in the Financial Crimes and AML space, and in this role you will develop strategies and lead key workstreams to deliver actionable analytics to leaders throughout the Block business and tell the story of our Compliance program to regulators and external parties. Focused on quantifying compliance risks and driving effectiveness, you will enable Block to redefine the world's relationship with money. You Will Lead data strategy for our regulatory engagements - from ETL development to source data validation to analysis Connect the dots between regulatory expectations, commitments, and the Compliance and Product roadmaps in order to influence strategy Harness raw data to educate internal and external partners on the impact of new regulation, policies, or environmental changes to our compliance program and the Block platforms. Collaborate with partners from legal to engineering to inform strategic builds of essential compliance program elements Establish yourself as a leader in the organization, by connecting insights to action through expert communication and cross-functional alignment Leverage your subject matter expertise to educate, coach and influence in and out of the organization with a focus on contributing to the overall, long-term success of Block Lead multiple high-impact workstreams, through ability to seamlessly navigate levels of abstraction in written and verbal communications. You Have 8+ years of related experience with a Bachelor’s degree; or 6+ years and a Master’s degree; or equivalent work experience. 5+ years of Compliance/AML experience Expert level abilities in SQL and data analysis/visualization tools (i.e. Tableau, Looker) Expert in ETL development Proven track record solving large and complex problems without clear answers, using deep and broad technical expertise Vision to define problems and manage projects in a fast-paced, evolving organization Experience bringing data to life for any audience through written and verbal communication and data visualization. Impeccable attention to detail and polish Even Better (but not required): CAMS or other AML certification Experience in the FinTech or consulting industry or with financial crimes compliance systems, technologies and processes. Experience with automation using Python, R or Prefect Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $171,800 — $257,600 USD Zone B: $159,800 — $239,600 USD Zone C: $151,200 — $226,800 USD Zone D: $142,600 — $213,800 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1100111101001</v>
       </c>
     </row>
@@ -620,21 +630,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>New York, NY (HQ)</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/bca0346c-b843-4795-96df-6091f51e421b</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>ABOUT RAMP
 Ramp is building the smart infrastructure for finance teams, embedded in the transaction flow of every dollar a business spends. We automate how over $200B in annualized spend flows in and out of 70,000+ companies: authorizing payments, flagging risk, categorizing spend, and closing books.
@@ -696,18 +711,18 @@
 Ramp Applicant Privacy Notice https://ramp.com/legal/applicant-privacy-notice</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1100101000001</v>
       </c>
     </row>
@@ -749,21 +764,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>New York, NY (HQ)</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/e577622f-6657-4e53-8941-b3a774b04448</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>ABOUT RAMP
 Ramp is building the smart infrastructure for finance teams, embedded in the transaction flow of every dollar a business spends. We automate how over $200B in annualized spend flows in and out of 70,000+ companies: authorizing payments, flagging risk, categorizing spend, and closing books.
@@ -829,18 +849,18 @@
 Ramp Applicant Privacy Notice https://ramp.com/legal/applicant-privacy-notice</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1100101000000</v>
       </c>
     </row>
@@ -882,21 +902,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>New York, NY (HQ)</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/ramp/16fb536d-fe10-4ea7-8956-d6d0cbddd6f5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>ABOUT RAMP
 Ramp is building the smart infrastructure for finance teams, embedded in the transaction flow of every dollar a business spends. We automate how over $200B in annualized spend flows in and out of 70,000+ companies: authorizing payments, flagging risk, categorizing spend, and closing books.
@@ -965,18 +990,18 @@
 Ramp Applicant Privacy Notice https://ramp.com/legal/applicant-privacy-notice</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1100100001000</v>
       </c>
     </row>
@@ -1018,37 +1043,42 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>New York, NY, United States of America</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5239527008?gh_jid=5239527008</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>It all started with an idea at Block in 2013. Initially built to take the pain out of peer-to-peer payments, Cash App has gone from a simple product with a single purpose to a dynamic ecosystem, developing unique financial products, including Afterpay/Clearpay, to provide a better way to send, spend, invest, borrow and save to our 50+ million monthly active customers. We want to redefine the world’s relationship with money to make it more relatable, instantly available, and universally accessible. Today, Cash App has thousands of employees working globally across office and remote locations, with a culture geared toward innovation, collaboration and impact. We’ve been a distributed team since day one, and many of our roles can be done remotely from the countries where Cash App operates. No matter the location, we tailor our experience to ensure our employees are creative, productive, and happy. The Role As a Senior Data Scientist focusing on AI &amp; Model Risk, you will lead and coordinate AI risk assessments for Generative AI and Large Language Model use cases, applying Model Risk Management principles to ensure safe, compliant, and responsible deployment. This role sits at the intersection of Model Risk Management and AI Governance, with close coordination with Information Security, Compliance, and Legal stakeholders. You will tackle complex and ambiguous challenges, applying sound judgment to select appropriate methodologies and drive risk-based decisions with minimal day-to-day oversight. You will partner with senior stakeholders across Risk, Engineering, Legal, Compliance, and Information Security to drive assessment outcomes and continuously strengthen governance practice. This role puts you at the center of an innovative team within SFS that's actively shaping how AI risk management works in practice; Operationalizing principles into processes that enable safe, effective AI deployment. If you're excited by the challenge of shaping how AI gets deployed safely and responsibly in financial services, this is the place to be. You Will Lead end-to-end AI Risk Assessments for generative AI and LLM use cases across the Bank; Embedding in Block's enterprise-wide GenAI review process, coordinating cross-functional SMEs (Legal, Compliance, InfoSec, Data Governance, MRM, ERM, BRC, TPRM, Financial Crimes), and managing timelines to ensure reviews are completed within SLA. Review AI system design and documentation; Including retrieval sources, assumptions, limitations, fallback plans, guardrail configurations, and change management procedures — across banking use cases such as fraud detection, BSA/AML compliance, credit decisioning, and customer-facing applications, ensuring governance controls are commensurate with each use case's risk profile. Assess pre-deployment testing for adequacy inclusive of output integrity, hallucination detection, boundary and edge case testing, ethical and safety guardrails, bias testing, A/B testing, volume testing, and UAT — designing and conducting independent testing as needed. Evaluate ongoing monitoring plans for comprehensiveness - including accuracy, hallucination rates, drift detection, sensitive data controls, reliability metrics, CSAT, acceptable performance ranges, and documented remediation procedures. Develop and maintain templates, tools, and procedures to support the effectiveness and scalability of the AI Risk Governance Program. Monitor the evolving regulatory landscape for AI in banking — including FFIEC IT Examination Handbook standards, FDIC Financial Institution Letters, interagency statements, and the anticipated RFI on AI model risk management referenced in SR 26-2 — and incorporate emerging guidance into the AI risk governance program; support SFS's response to regulatory inquiries as needed. You Have A minimum of 5 years of related experience with a Bachelor’s degree in a quantitative field; or 3 years and a Master’s degree; or a PhD without experience; or equivalent work experience in risk management, model risk management, or AI risk management Proficiency in Python or similar languages for evaluating AI system behavior, writing test scripts, or analyzing model outputs Strong understanding of generative AI architectures; Including LLMs, transformer models, RAG systems, and agentic AI, plus hands-on experience interacting with and critically evaluating these systems, sufficient to assess design decisions, output quality, and limitations Understanding of interagency model risk management principles, including SR 26-2 Knowledge of AI testing methodologies, ex. functional testing, bias testing, adversarial testing, and performance monitoring plus familiarity with data privacy and security principles (encryption, access controls, data classification) Excellent written and verbal communication and the ability to translate complex technical AI concepts for non-technical stakeholders, senior management, and regulators Strong analytical judgment with the ability to manage multiple concurrent assessments, prioritize effectively, and drive risk-based decisions with minimal day-to-day oversight Nice to Have Master's degree in AI/ML, Cybersecurity, Data Science, or related field Familiarity with AI governance frameworks (NIST AI RMF, ISO 42001, or equivalent) and the FFIEC IT Examination Handbooks Experience with AI governance tools and platforms (model registries, monitoring dashboards, risk scoring systems) Experience with explainability tools (SHAP, LIME, attention visualization) Certifications: CRISC, PRM, FRM, or AI-specific certifications such as NIST AI RMF practitioner or ISO 42001 Lead Implementer Prior experience in a second-line-of-defense or internal audit role at a bank or financial institution Experience developing AI risk governance frameworks in environments where prescriptive regulatory guidance does not yet exist Technologies We Use and Teach Block is investing heavily in AI, and our workflows are evolving accordingly. This creates a rare opportunity to work with emerging systems as they take shape, both leveraging them in practice and influencing how they are designed. The team is at the forefront of defining risk governance in an AI-first environment, with the goal of setting new industry standards. We're working to build a more inclusive economy where our customers have equal access to opportunity, and we strive to live by these same values in building our workplace. Block is an equal opportunity employer evaluating all employees and job applicants without regard to identity or any legally protected class. We will consider qualified applicants with arrest or conviction records for employment in accordance with state and local laws and "fair chance" ordinances. We believe in being fair, and are committed to an inclusive interview experience, including providing reasonable accommodations to disabled applicants throughout the recruitment process. We encourage applicants to share any needed accommodations with their recruiter, who will treat these requests as confidentially as possible. Want to learn more about what we're doing to build a workplace that is fair and square? Check out our I+D page . While there is no specific deadline to apply for this role, U.S. roles are typically open for an average of 55 days before being filled by a successful candidate. Please refer to the date listed at the top of this job page for when this role was first posted. Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $163,600 — $225,000 USD Zone B: $155,400 — $213,700 USD Zone C: $147,300 — $202,500 USD Zone D: $139,000 — $191,200 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1100100000001</v>
       </c>
     </row>
@@ -1090,33 +1120,38 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Remote Massachusetts</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>https://humana.wd5.myworkdayjobs.com/en-US/Humana_External_Career_Site/job/Remote-Massachusetts/Principal-Data-Engineer_R-421129</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1100000000000</v>
       </c>
     </row>
@@ -1158,21 +1193,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/toptal/a2cbc223-9e67-4c87-95b2-c72fdd6fa554</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>About Toptal
 Toptal is a global network of top talent in business, design, and technology that enables companies to scale their teams, on-demand. With $200+ million in annual revenue and team members based around the globe, Toptal is the world’s largest fully remote workforce.
@@ -1239,18 +1279,18 @@
 Applications are accepted on an ongoing basis. In the US, Toptal’s benefit offerings include participation in a 401(k) retirement plan; medical, dental, and vision health insurance plans; basic life insurance coverage and short-term and long-term disability coverage; access to flexible spending, dependent care, and health savings accounts; access to telehealth virtual doctors; an employee assistance program; and flexible paid time off.</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1010101001001</v>
       </c>
     </row>
@@ -1292,37 +1332,42 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Bay Area, CA, United States of America</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5098519008?gh_jid=5098519008</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Block is one company built from many blocks, all united by the same purpose of economic empowerment. The blocks that form our foundational teams — People, Finance, Counsel, Hardware, Information Security, Platform Infrastructure Engineering, and more — provide support and guidance at the corporate level. They work across business groups and around the globe, spanning time zones and disciplines to develop inclusive People policies, forecast finances, give legal counsel, safeguard systems, nurture new initiatives, and more. Every challenge creates possibilities, and we need different perspectives to see them all. Bring yours to Block. The Role The Staff Data Analyst will join the Block Compliance Analytics team chartered to put data at the center of the Compliance organization. You have a proven track record in the Financial Crimes and AML space, and in this role you will develop strategies and lead key workstreams to deliver actionable analytics to leaders throughout the Block business and tell the story of our Compliance program to regulators and external parties. Focused on quantifying compliance risks and driving effectiveness, you will enable Block to redefine the world's relationship with money. You Will Lead data strategy for our regulatory engagements - from ETL development to source data validation to analysis Connect the dots between regulatory expectations, commitments, and the Compliance and Product roadmaps in order to influence strategy Harness raw data to educate internal and external partners on the impact of new regulation, policies, or environmental changes to our compliance program and the Block platforms. Collaborate with partners from legal to engineering to inform strategic builds of essential compliance program elements Establish yourself as a leader in the organization, by connecting insights to action through expert communication and cross-functional alignment Leverage your subject matter expertise to educate, coach and influence in and out of the organization with a focus on contributing to the overall, long-term success of Block Lead multiple high-impact workstreams, through ability to seamlessly navigate levels of abstraction in written and verbal communications. You Have 8+ years of related experience with a Bachelor’s degree; or 6+ years and a Master’s degree; or equivalent work experience. 5+ years of Compliance/AML experience Expert level abilities in SQL and data analysis/visualization tools (i.e. Tableau, Looker) Expert in ETL development Proven track record solving large and complex problems without clear answers, using deep and broad technical expertise Vision to define problems and manage projects in a fast-paced, evolving organization Experience bringing data to life for any audience through written and verbal communication and data visualization. Impeccable attention to detail and polish Even Better (but not required): CAMS or other AML certification Experience in the FinTech or consulting industry or with financial crimes compliance systems, technologies and processes. Experience with automation using Python, R or Prefect Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $171,800 — $257,600 USD Zone B: $159,800 — $239,600 USD Zone C: $151,200 — $226,800 USD Zone D: $142,600 — $213,800 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1000111101001</v>
       </c>
     </row>
@@ -1364,37 +1409,42 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Denver, CO, United States of America</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5114793008?gh_jid=5114793008</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Block is one company built from many blocks, all united by the same purpose of economic empowerment. The blocks that form our foundational teams — People, Finance, Counsel, Hardware, Information Security, Platform Infrastructure Engineering, and more — provide support and guidance at the corporate level. They work across business groups and around the globe, spanning time zones and disciplines to develop inclusive People policies, forecast finances, give legal counsel, safeguard systems, nurture new initiatives, and more. Every challenge creates possibilities, and we need different perspectives to see them all. Bring yours to Block. The Role The Staff Data Analyst will join the Block Compliance Analytics team chartered to put data at the center of the Compliance organization. You have a proven track record in the Financial Crimes and AML space, and in this role you will develop strategies and lead key workstreams to deliver actionable analytics to leaders throughout the Block business and tell the story of our Compliance program to regulators and external parties. Focused on quantifying compliance risks and driving effectiveness, you will enable Block to redefine the world's relationship with money. You Will Lead data strategy for our regulatory engagements - from ETL development to source data validation to analysis Connect the dots between regulatory expectations, commitments, and the Compliance and Product roadmaps in order to influence strategy Harness raw data to educate internal and external partners on the impact of new regulation, policies, or environmental changes to our compliance program and the Block platforms. Collaborate with partners from legal to engineering to inform strategic builds of essential compliance program elements Establish yourself as a leader in the organization, by connecting insights to action through expert communication and cross-functional alignment Leverage your subject matter expertise to educate, coach and influence in and out of the organization with a focus on contributing to the overall, long-term success of Block Lead multiple high-impact workstreams, through ability to seamlessly navigate levels of abstraction in written and verbal communications. You Have 8+ years of related experience with a Bachelor’s degree; or 6+ years and a Master’s degree; or equivalent work experience. 5+ years of Compliance/AML experience Expert level abilities in SQL and data analysis/visualization tools (i.e. Tableau, Looker) Expert in ETL development Proven track record solving large and complex problems without clear answers, using deep and broad technical expertise Vision to define problems and manage projects in a fast-paced, evolving organization Experience bringing data to life for any audience through written and verbal communication and data visualization. Impeccable attention to detail and polish Even Better (but not required): CAMS or other AML certification Experience in the FinTech or consulting industry or with financial crimes compliance systems, technologies and processes. Experience with automation using Python, R or Prefect Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $171,800 — $257,600 USD Zone B: $159,800 — $239,600 USD Zone C: $151,200 — $226,800 USD Zone D: $142,600 — $213,800 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>MT</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1000111101001</v>
       </c>
     </row>
@@ -1436,37 +1486,42 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Bay Area, CA, United States of America</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5318944008?gh_jid=5318944008</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Since we opened our doors in 2009, the world of commerce has evolved immensely, and so has Square. After enabling anyone to take payments and never miss a sale, we saw sellers stymied by disparate, outmoded products and tools that wouldn’t work together. So we expanded into software and started building integrated, omnichannel solutions – to help sellers sell online, manage inventory, offer buy now, pay later functionality, book appointments, engage loyal buyers, and hire and pay staff. Across it all, we’ve embedded financial services tools at the point of sale, so merchants can access a business loan and manage their cash flow in one place. Afterpay furthers our goal to provide omnichannel tools that unlock meaningful value and growth, enabling sellers to capture the next generation shopper, increase order sizes, and compete at a larger scale. Today, we are a partner to sellers of all sizes – large, enterprise-scale businesses with complex operations, sellers just starting, as well as merchants who began selling with Square and have grown larger over time. As our sellers grow, so do our solutions. There is a massive opportunity in front of us. We’re building a significant, meaningful, and lasting business, and we are helping sellers worldwide do the same. The Role Square's Sales organization is where we're placing our biggest bets, and the go-to-market (GTM) Data Science team sits at the heart of that growth engine. Reporting to the Sales Data Science lead, you'll own a mature subdomain of our Sales function and contribute across the full channel, alongside peers in Sales Data Science (DS) and the wider GTM Data Science org. The role is a rare combination: you'll be a trusted analytics leader who sales executives turn to for the ground truth on business performance, and a hands-on data scientist who solves big, ambiguous problems end to end. This is a DS team on the front lines of AI, one that uses agents daily to clear away the mundane and free up time for the high-impact, technically challenging work that moves the business forward. You'll grow here: there's no shortage of hard problems, plenty of sharp colleagues to learn from, and the leverage to scale your impact well beyond your own domain. You Will Own performance measurement for your subdomain: monitoring the metrics that matter (wins, new revenue, funnel conversion, rep productivity), reporting against plan, and presenting the story in business reviews with sales leadership Lead investigations into performance questions ("why is X down?", "how can we improve Y?"), decomposing KPIs from first principles and designing experiments to test what actually works Take on large, ambiguous projects autonomously: scoping the problem, finding the right data, thinking critically about what it can and can't tell you, and landing the results with stakeholders Own and evolve your subdomain's data foundation, and partner with Sales DS peers on shared metrics, attribution logic, and cross-cutting analyses Translate data into business context: telling the story behind the numbers, pushing back on hypotheses with evidence, and building trust with senior sales, finance, and operations leaders Work AI-natively: use agents throughout your workflow and pioneer new ways of applying AI to the hardest problems in the sales domain Build self-serve dashboards and datasets that let the sales org answer its own questions Raise the bar for the team's analytical rigor, communication, and AI-enabled ways of working You Have Minimum of 8 years of related experience with a Bachelor’s degree; or 6 years and a Master’s degree; or a PhD with 3 years experience; or equivalent experience Advanced SQL and strong Python; comfort owning the full stack from ETL to analysis to visualization Strong statistical foundations: experiment design, causal inference, funnel and cohort analysis, and forecasting; you can interpret results with rigor and explain the concepts behind them A track record of running large projects end to end with minimal direction; you're the person leadership trusts when the numbers matter Strong critical thinking: you know when to move fast and when to slow down on a problem with big consequences, and you pressure-test your own conclusions Exceptional communication: you can present performance to executives, translate technical nuance for non-technical partners, and write analysis documents that stand on its own Enthusiasm for building with AI, and curiosity about how far it can be pushed in data science work Curiosity about unfamiliar data and how sales organizations actually work, and the empathy to partner well with the people on the frontline Nice to have, but not required: Prior experience supporting sales, GTM, or revenue organizations Familiarity with fintech, payments, or the SMB merchant space We value strong fundamentals and curiosity over industry background; we'll teach you our domain. Technologies We Use and Teach SQL, Snowflake, Databricks, Python (Pandas, NumPy) Looker, Omni, Airflow, dbt-style ETL patterns Agentic AI: agent skills and bots, automated reporting workflows, in-house tooling Salesforce and the modern GTM data stack A/B, matched-market, and causal testing Pay Transparency: Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate's starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location's zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: ($198,000 - $297,000) Zone B: ($188,100 - $282,100) Zone C: ($178,200 - $267,400) Zone D: ($168,300- $252,500) Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1000101101001.01</v>
       </c>
     </row>
@@ -1508,37 +1563,42 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Bay Area, CA, United States of America</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5281312008?gh_jid=5281312008</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>It all started with an idea at Block in 2013. Initially built to take the pain out of peer-to-peer payments, Cash App has gone from a simple product with a single purpose to a dynamic ecosystem, developing unique financial products, including Afterpay/Clearpay, to provide a better way to send, spend, invest, borrow and save to our 50+ million monthly active customers. We want to redefine the world’s relationship with money to make it more relatable, instantly available, and universally accessible. Today, Cash App has thousands of employees working globally across office and remote locations, with a culture geared toward innovation, collaboration and impact. We’ve been a distributed team since day one, and many of our roles can be done remotely from the countries where Cash App operates. No matter the location, we tailor our experience to ensure our employees are creative, productive, and happy. The Role As a Data Engineer you will handle everything from data architecture and modeling to data pipeline tooling and dashboarding. You will enable other compliance and risk teams to make impactful business decisions by laying the foundation of our large and unique datasets that span across multiple products. This role will support compliance or risk product data engineering teams. The Compliance Data Engineering team at Block supports the detection and reporting of suspicious financial crimes activity across Cash App, Square, and Afterpay. We work globally with partners in business, engineering, counsel, and product to provide a safe user experience for our customers while minimizing and potentially eliminating bad activity on our platform. The Risk Product Data Engineering team at Block builds reliable data foundations that help protect customers across Cash App, Square, and Afterpay. We partner with product, engineering, compliance, and legal teams to support risk detection, reporting, instrumentation, and ML-ready datasets across critical domains including identity, account access, eligibility, controls, and disputes. You Will Lead the creation and optimization of existing data models through AI code generation on eventing, customer level, and process level data. Standardize business and product metric definitions in curated and optimized datasets, and develop data dictionaries and other related documentation. Build monitoring to assess data quality and lineage and on top build AI agents for false positive reduction and automated resolution. Participate in on-call rotation, monitor daily execution, diagnose and log issues, and fix business critical pipelines to ensure SLAs are met with internal stakeholders. Automate this process through AI agents to focus human effort on highest priority tasks. Work with non-technical partners and product teams to understand their needs, translate business requirements into applicable data requirements, and come up with automated end-to-end solutions. You Have A minimum of 10 years of related experience with a Bachelor’s degree; or 8 years and a Master’s degree; or equivalent experience. High proficiency in SQL, Python, and Dbt Experience designing medium-to-large data engineering solutions and responsible for the entire lifecycle of projects including scoping, design, development, testing, deployment, and documentation Experience with ETL scheduling technologies with dependency checking, such as Airflow or Prefect, as well as Experience in schema design and dimensional data modeling Experience with setting up data quality and data lineage monitoring Experience with data driven decisions through AI and agentic automation Technologies We Use and Teach Snowflake Databricks Dbt Github Airflow Prefect Omni Terraform We’re working to build a more inclusive economy where our customers have equal access to opportunity, and we strive to live by these same values in building our workplace. Block is an equal opportunity employer evaluating all employees and job applicants without regard to identity or any legally protected class. We will consider qualified applicants with arrest or conviction records for employment in accordance with state and local laws and “fair chance” ordinances. We believe in being fair, and are committed to an inclusive interview experience, including providing reasonable accommodations to disabled applicants throughout the recruitment process. We encourage applicants to share any needed accommodations with their recruiter, who will treat these requests as confidentially as possible. Want to learn more about what we’re doing to build a workplace that is fair and square? Check out our I+D page . While there is no specific deadline to apply for this role, U.S. roles are typically open for an average of 55 days before being filled by a successful candidate. Please refer to the date listed at the top of this job page for when this role was first posted. Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $198,000 — $297,000 USD Zone B: $188,100 — $282,100 USD Zone C: $178,200 — $267,400 USD Zone D: $168,300 — $252,500 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1000101100001.01</v>
       </c>
     </row>
@@ -1580,37 +1640,42 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>Bay Area, CA, United States of America</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5198102008?gh_jid=5198102008</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Block builds simple, powerful tools that make progress towards an economy that’s truly open to all. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Join us. The Role We’re hiring Senior and Staff Machine Learning Engineers to join Block’s Risk Machine Learning organization, where teams apply ML at massive scale to detect, prevent, and reduce fraud and abuse across Cash App and Square. This opening supports multiple senior-level roles, with team placement determined through a collaborative matching process based on your experience, interests, and current business needs. Today, we’re growing teams focused fraud &amp; abuse prevention, merchant risk, credit underwriting (consumer &amp; commercial lending), buy-now-pay-later decisioning, AI-powered customer support &amp; conversational AI, agentic automation for investigations, and model risk governance. We'd love to hear from you whether your background is in adversarial ML, NLP/LLMs, credit modeling, or model validation. Across teams, your work will directly protect our ecosystem, reduce financial loss, and enable safe, seamless financial experiences for millions of customers, sellers, and families. You Will Partner with product, engineering, data science, policy, and operations to design and productionize ML-driven risk solutions at scale Own end-to-end machine learning systems — from problem definition and modeling to deployment, monitoring, and iteration Lead technical decision-making within your workstreams and influence ML strategy and planning Build tooling and processes that improve the speed, reliability, and impact of the ML development lifecycle Apply state-of-the-art modeling techniques and third-party data sources to improve detection and decision-making Investigate emerging fraud, abuse, and risk patterns to proactively inform product safeguards and policy Collaborate closely with ML platform and engineering teams to ensure models operate reliably in real time and at scale You Have 8+ years of industry experience in machine learning, applied AI, or related fields Bachelor’s degree in a quantitative field (Computer Science, Engineering, Statistics, Physics, Applied Math); Master’s or PhD preferred Proven experience independently designing, deploying, and maintaining ML solutions in production Strong familiarity with techniques such as tree-based models, deep learning, transfer learning, or reinforcement learning Experience influencing technical direction and collaborating with cross-functional partners at scale Strong communication skills, sound judgment, and an ownership mindset Curiosity and alignment with Block’s mission of economic empowerment Technologies We Use and Teach Python (NumPy, Pandas, scikit-learn, XGBoost, PyTorch, TensorFlow/Keras) PySpark, MLflow, workflow orchestration tools (Airflow, Prefect) GCP (Vertex AI), AWS Snowflake, MySQL, Tableau, Mode Containerization, CI/CD, and production ML best practices Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1000101001001.1</v>
       </c>
     </row>
@@ -1652,37 +1717,42 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Bay Area, CA, United States of America</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5248631008?gh_jid=5248631008</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Block builds simple, powerful tools that make progress towards an economy that’s truly open to all. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Join us. The Role As a Staff Applied Machine Learning Engineer focused on Intelligent Data, Signals &amp; Systems, you will build production ML systems that transform customer behavior, product context, model outputs, and feedback loops into trusted signals used by recommendations, ranking, risk-aware decisioning, growth, and customer intelligence systems. This role centers on customer intelligence and reusable model-derived signal systems: ranking and retrieval, recommendations, search, propensity and churn/LTV, next-best-action decisioning, experimentation, and feedback loops. These systems help product, growth, fraud, and risk teams make better decisions with clear freshness, provenance, confidence, and evaluation guarantees. The work combines production ML systems with composable signal interfaces that can be consumed by product surfaces, decision engines, internal tools, and verified AI-assisted workflows. The role is flexible across Applied ML Engineering domains while still requiring deep expertise. You Will Build and operate production ML systems that turn customer and product context into trusted signals, rankings, recommendations, and decision capabilities. Design production data and signal contracts that define intended use, freshness, provenance, confidence, eligibility, and calibration for downstream consumers. Own ranking, retrieval, recommendation, search, propensity, and next-best-action systems end to end, from feature and candidate generation through serving, experimentation, monitoring, and feedback loops. Evaluate customer and business impact beyond short-term conversion, including trust, fairness, access, risk, compliance, long-term engagement, and segment-level performance. Partner across product, growth, data, platform, modeling, risk, and compliance to translate ambiguous goals into measurable ML system designs. Use AI and agents to accelerate development, analysis, testing, documentation, and operations while exposing reusable capabilities to product services, internal tools, and AI-assisted workflows. You Have 12+ years building and operating production software and ML systems for business-critical products. Deep expertise in intelligent systems such as ranking/retrieval, recommendations, search, personalization, growth and lifecycle ML, customer intelligence, propensity/churn/LTV, next-best-action, or model-derived risk signals. Strong production ML judgment across feature pipelines, model serving, experimentation, monitoring, feedback loops, online/offline consistency, and reliable signal interfaces. Ability to evaluate impact beyond short-term conversion, including trust, fairness, access, risk, compliance, and long-term engagement. Experience using AI-assisted engineering tools with appropriate verification, testing, and review for customer-impacting systems. Nice to Have Experience with semantic retrieval, embeddings, two-tower models, graph features, LLM-powered retrieval or decision systems, entity resolution, or real-time personalization. Experience with experimentation, online evaluation, interleaving, counterfactual evaluation, multi-objective optimization, or long-term holdouts. Experience building reusable feature/signal platforms, decision services, customer intelligence layers, model-derived data products, or agent-assisted operations. Technologies We Use and Teach We do not expect candidates to have used our exact stack. We do expect strong production engineering fundamentals, deep domain expertise in intelligent ML systems, and judgment about how ML-derived signals should be used safely in customer-impacting products. Examples of technologies and methods include: Python, Java, Kotlin, SQL. TensorFlow, PyTorch, XGBoost/LightGBM, ranking/retrieval systems, embeddings, semantic search, recommendation frameworks. Event streams, batch pipelines, feature stores, model-serving infrastructure, workflow orchestration, experimentation systems, and data warehouses/lakehouses. Cloud infrastructure, Kubernetes, observability tooling, coding agents, evaluation harnesses, and agent-assisted operations tooling. We’re working to build a more inclusive economy where our customers have equal access to opportunity, and we strive to live by these same values in building our workplace. Block is an equal opportunity employer evaluating all employees and job applicants without regard to identity or any legally protected class. We will consider qualified applicants with arrest or conviction records for employment in accordance with state and local laws and “fair chance” ordinances. We believe in being fair, and are committed to an inclusive interview experience, including providing reasonable accommodations to disabled applicants throughout the recruitment process. We encourage applicants to share any needed accommodations with their recruiter, who will treat these requests as confidentially as possible. Want to learn more about what we’re doing to build a workplace that is fair and square? Check out our I+D page . While there is no specific deadline to apply for this role, U.S. roles are typically open for an average of 55 days before being filled by a successful candidate. Please refer to the date listed at the top of this job page for when this role was first posted. Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $276,800 — $415,200 USD Zone B: $276,800 — $415,200 USD Zone C: $276,800 — $415,200 USD Zone D: $276,800 — $415,200 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1000101000001</v>
       </c>
     </row>
@@ -1724,37 +1794,42 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Bay Area, CA, United States of America</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5221040008?gh_jid=5221040008</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>It all started with an idea at Block in 2013. Initially built to take the pain out of peer-to-peer payments, Cash App has gone from a simple product with a single purpose to a dynamic ecosystem, developing unique financial products, including Afterpay/Clearpay, to provide a better way to send, spend, invest, borrow and save to our 50+ million monthly active customers. We want to redefine the world’s relationship with money to make it more relatable, instantly available, and universally accessible. Today, Cash App has thousands of employees working globally across office and remote locations, with a culture geared toward innovation, collaboration and impact. We’ve been a distributed team since day one, and many of our roles can be done remotely from the countries where Cash App operates. No matter the location, we tailor our experience to ensure our employees are creative, productive, and happy. The Role As a Senior Data Scientist focusing on AI &amp; Model Risk, you will lead and coordinate AI risk assessments for Generative AI and Large Language Model use cases, applying Model Risk Management principles to ensure safe, compliant, and responsible deployment. This role sits at the intersection of Model Risk Management and AI Governance, with close coordination with Information Security, Compliance, and Legal stakeholders. You will tackle complex and ambiguous challenges, applying sound judgment to select appropriate methodologies and drive risk-based decisions with minimal day-to-day oversight. You will partner with senior stakeholders across Risk, Engineering, Legal, Compliance, and Information Security to drive assessment outcomes and continuously strengthen governance practice. This role puts you at the center of an innovative team within SFS that's actively shaping how AI risk management works in practice; Operationalizing principles into processes that enable safe, effective AI deployment. If you're excited by the challenge of shaping how AI gets deployed safely and responsibly in financial services, this is the place to be. You Will Lead end-to-end AI Risk Assessments for generative AI and LLM use cases across the Bank; Embedding in Block's enterprise-wide GenAI review process, coordinating cross-functional SMEs (Legal, Compliance, InfoSec, Data Governance, MRM, ERM, BRC, TPRM, Financial Crimes), and managing timelines to ensure reviews are completed within SLA. Review AI system design and documentation; Including retrieval sources, assumptions, limitations, fallback plans, guardrail configurations, and change management procedures — across banking use cases such as fraud detection, BSA/AML compliance, credit decisioning, and customer-facing applications, ensuring governance controls are commensurate with each use case's risk profile. Assess pre-deployment testing for adequacy inclusive of output integrity, hallucination detection, boundary and edge case testing, ethical and safety guardrails, bias testing, A/B testing, volume testing, and UAT — designing and conducting independent testing as needed. Evaluate ongoing monitoring plans for comprehensiveness - including accuracy, hallucination rates, drift detection, sensitive data controls, reliability metrics, CSAT, acceptable performance ranges, and documented remediation procedures. Develop and maintain templates, tools, and procedures to support the effectiveness and scalability of the AI Risk Governance Program. Monitor the evolving regulatory landscape for AI in banking — including FFIEC IT Examination Handbook standards, FDIC Financial Institution Letters, interagency statements, and the anticipated RFI on AI model risk management referenced in SR 26-2 — and incorporate emerging guidance into the AI risk governance program; support SFS's response to regulatory inquiries as needed. You Have A minimum of 5 years of related experience with a Bachelor’s degree in a quantitative field; or 3 years and a Master’s degree; or a PhD without experience; or equivalent work experience in risk management, model risk management, or AI risk management Proficiency in Python or similar languages for evaluating AI system behavior, writing test scripts, or analyzing model outputs Strong understanding of generative AI architectures; Including LLMs, transformer models, RAG systems, and agentic AI, plus hands-on experience interacting with and critically evaluating these systems, sufficient to assess design decisions, output quality, and limitations Understanding of interagency model risk management principles, including SR 26-2 Knowledge of AI testing methodologies, ex. functional testing, bias testing, adversarial testing, and performance monitoring plus familiarity with data privacy and security principles (encryption, access controls, data classification) Excellent written and verbal communication and the ability to translate complex technical AI concepts for non-technical stakeholders, senior management, and regulators Strong analytical judgment with the ability to manage multiple concurrent assessments, prioritize effectively, and drive risk-based decisions with minimal day-to-day oversight Nice to Have Master's degree in AI/ML, Cybersecurity, Data Science, or related field Familiarity with AI governance frameworks (NIST AI RMF, ISO 42001, or equivalent) and the FFIEC IT Examination Handbooks Experience with AI governance tools and platforms (model registries, monitoring dashboards, risk scoring systems) Experience with explainability tools (SHAP, LIME, attention visualization) Certifications: CRISC, PRM, FRM, or AI-specific certifications such as NIST AI RMF practitioner or ISO 42001 Lead Implementer Prior experience in a second-line-of-defense or internal audit role at a bank or financial institution Experience developing AI risk governance frameworks in environments where prescriptive regulatory guidance does not yet exist Technologies We Use and Teach Block is investing heavily in AI, and our workflows are evolving accordingly. This creates a rare opportunity to work with emerging systems as they take shape, both leveraging them in practice and influencing how they are designed. The team is at the forefront of defining risk governance in an AI-first environment, with the goal of setting new industry standards. We're working to build a more inclusive economy where our customers have equal access to opportunity, and we strive to live by these same values in building our workplace. Block is an equal opportunity employer evaluating all employees and job applicants without regard to identity or any legally protected class. We will consider qualified applicants with arrest or conviction records for employment in accordance with state and local laws and "fair chance" ordinances. We believe in being fair, and are committed to an inclusive interview experience, including providing reasonable accommodations to disabled applicants throughout the recruitment process. We encourage applicants to share any needed accommodations with their recruiter, who will treat these requests as confidentially as possible. Want to learn more about what we're doing to build a workplace that is fair and square? Check out our I+D page . While there is no specific deadline to apply for this role, U.S. roles are typically open for an average of 55 days before being filled by a successful candidate. Please refer to the date listed at the top of this job page for when this role was first posted. Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $163,600 — $225,000 USD Zone B: $155,400 — $213,700 USD Zone C: $147,300 — $202,500 USD Zone D: $139,000 — $191,200 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1000100000001</v>
       </c>
     </row>
@@ -1796,37 +1871,42 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>Seattle, WA, United States of America</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/5198105008?gh_jid=5198105008</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Block builds simple, powerful tools that make progress towards an economy that’s truly open to all. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Join us. The Role Block's Support ML Modeling team is a central driver of innovation in customer support experiences across our entire ecosystem—including Cash App, Square, and other business units. We are dedicated to advancing the state of intelligent, automated support through machine learning and generative AI. From customer-facing chatbots to smart internal tools for agents, our team builds high-impact, scalable systems that improve support quality, efficiency, and accessibility. We're building the future of support at Block: one powered by AI, voice interfaces, and smart automation. We're looking for candidates with a passion for intelligent systems, practical ML experience, and a desire to build product-driven solutions. Our ideal candidate is a leader in the field, with a proven track record of building ML systems that can accelerate our ability to scale our conversational AI initiatives. You Will Lead the end-to-end delivery of multiple ML initiatives, from planning and design through rollout, documentation, and long-term maintenance Partner strategically with risk, product, engineering, design, and operations leaders to define and drive long term ML roadmaps, informed by domain expertise and industry trends Guide the team’s direction, identifying new ML/AI opportunities and advising leadership on strategic tradeoffs and opportunities Drive R&amp;D efforts exploring next-generation chatbot architectures using LLMs, RAG, fine-tuning, and real-time inference Design, deploy, and maintain ML models powering conversational agents including support chatbots across Cash App, Square, and other Block products Develop ML-powered tools and real time recommendation systems that enhance support agent effectiveness and customer outcomes Act as the technical representative for your team’s systems and programs, clearly communicating work and results to stakeholders, cross-functional partners, and external audiences You Have 10+ years of experience in machine learning, applied AI, or product ML roles, with deep technical expertise Demonstrated leadership capabilities, with the ability to influence and align cross-functional teams while directly shaping the work of peers through communication, context sharing, and technical guidance A track record of delivering organizational wide impact, shaping systems, frameworks, or initiatives that raise the bar across multiple teams or functions Proven ability to ship end to end ML features from problem framing through deployment and long-term maintenance Demonstrated experience with language models, dialog systems, or generative AI in production Strong foundation in NLP, deep learning, or ML infrastructure best practices. Excellent communication skills, with the ability to represent the team’s work to leadership and stakeholders Enthusiasm for R&amp;D and pushing the boundaries of applied AI to transform conversational systems Technologies We Use and Teach Python, PyTorch, TensorFlow, or JAX We're working to build a more inclusive economy where our customers have equal access to opportunity, and we strive to live by these same values in building our workplace. Block is an equal opportunity employer evaluating all employees and job applicants without regard to identity or any legally protected class. We will consider qualified applicants with arrest or conviction records for employment in accordance with state and local laws and “fair chance” ordinances. We believe in being fair, and are committed to an inclusive interview experience, including providing reasonable accommodations to disabled applicants throughout the recruitment process. We encourage applicants to share any needed accommodations with their recruiter, who will treat these requests as confidentially as possible. Want to learn more about what we're doing to build a workplace that is fair and square? Check out our I+D page . Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $276,800 — $415,200 USD Zone B: $276,800 — $415,200 USD Zone C: $276,800 — $415,200 USD Zone D: $276,800 — $415,200 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1000100000001</v>
       </c>
     </row>
@@ -1868,29 +1948,34 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Remote Nationwide</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>https://humana.wd5.myworkdayjobs.com/en-US/Humana_External_Career_Site/job/Remote-Nationwide/Actuary--Analytics-Forecasting_R-421828</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>1</v>
       </c>
       <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1000000000000</v>
       </c>
     </row>
@@ -1932,37 +2017,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>New York, NY, United States of America</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>http://block.xyz/careers/jobs/4963850008?gh_jid=4963850008</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Block is one company built from many blocks, all united by the same purpose of economic empowerment. The blocks that form our foundational teams — People, Finance, Counsel, Hardware, Information Security, Platform Infrastructure Engineering, and more — provide support and guidance at the corporate level. They work across business groups and around the globe, spanning time zones and disciplines to develop inclusive People policies, forecast finances, give legal counsel, safeguard systems, nurture new initiatives, and more. Every challenge creates possibilities, and we need different perspectives to see them all. Bring yours to Block. The Role Block's Advanced Insights and Modeling (AIM) team is an intellectually diverse group of machine learning modelers, data scientists, former strategy consultants, and data engineers. We apply cutting-edge AI, graph analytics, and machine learning to solve high-impact business problems for Block's executive leadership. Within this team, the Product group owns the end-to-end lifecycle of predictive models that serve stakeholders across Block — including Finance, Marketing, Sales, Legal, and Treasury. The product manager partners closely with Machine Learning engineers (MLE) to scope problems and data strategy and ensure successful model development, validation, deployment, and adoption. We continuously monitor model performance, share results and insights with business partners, and iterate to keep our tools trusted and relevant across a diverse set of use cases. We're looking for a strategic, analytically rigorous product leader who can operate at 10,000 feet while diving deep into the data. This role blends traditional product management with hands-on data science — you'll frame the business problem, shape the data strategy, and partner with ML engineers to deliver from conception to adoption. What You'll Do Problem Framing &amp; Product Strategy Own the forecasting product roadmap end-to-end — from problem definition through launch and iteration Define business context, success metrics, and constraints that keep work aligned with strategic goals Serve as the source of truth for model decisions; maintain clear documentation as systems evolve Manage project flow: prioritization, timelines, dependencies, and cross-functional alignment Data &amp; Signal Engineering Partner with ML engineers to ensure models are grounded in a clear, well-articulated understanding of the data Conduct in-depth data analysis to inform model design — segmentation, feature engineering, and evaluation strategy Leverage AI tools to explore data, generate hypotheses, accelerate analysis, and synthesize insights Analyze forecast results to identify trends, variances, and actionable recommendations for model performance Stakeholder Communication &amp; Adoption Translate complex analytical concepts for diverse audiences — executives, finance partners, technical MLEs, and marketing teams Drive adoption through in-product education, documentation, and feature rollout strategies Build relationships across Block to understand user needs and evangelize forecasting capabilities What You Bring 6+ years in product management, management consulting, data science, model analytics or a hybrid analytical role Hands-on SQL proficiency and experience with Python (or R) for data analysis Strong understanding of forecasting models, time-series analysis, and ML applications Experience in financial services, fintech, or consumer finance — you understand how macroeconomic shifts and monetary policy influence consumer behavior Executive presence — you can distill complex topics into clear, concise narratives for technical and non-technical audiences alike Proven ability to manage multiple workstreams, drive alignment, and deliver in ambiguous, fast-moving environments Comfort operating at both the strategic level (roadmap, stakeholder management) and in the weeds (data exploration, model evaluation) Prior experience at strategy consulting firm or in a cross-functional analytics/strategy role at a fintech or technology company Bachelor's or Master's degree in Business, Economics, Statistics, Computer Science, or a quantitative field Familiarity with our stack: SQL, Python, GitHub, Databricks, Claude We’re working to build a more inclusive economy where our customers have equal access to opportunity, and we strive to live by these same values in building our workplace. Block is an equal opportunity employer evaluating all employees and job applicants without regard to identity or any legally protected class. We will consider qualified applicants with arrest or conviction records for employment in accordance with state and local laws and “fair chance” ordinances. We believe in being fair, and are committed to an inclusive interview experience, including providing reasonable accommodations to disabled applicants throughout the recruitment process. We encourage applicants to share any needed accommodations with their recruiter, who will treat these requests as confidentially as possible. Want to learn more about what we’re doing to build a workplace that is fair and square? Check out our I+D page . While there is no specific deadline to apply for this role, U.S. roles are typically open for an average of 55 days before being filled by a successful candidate. Please refer to the date listed at the top of this job page for when this role was first posted. Block takes a market-based approach to pay, and pay may vary depending on your location. U.S. locations are categorized into one of four zones based on a cost of labor index for that geographic area. The successful candidate’s starting pay will be determined based on job-related skills, experience, qualifications, work location, and market conditions. These ranges may be modified in the future. To find a location’s zone designation, please refer to this resource . If a location of interest is not listed, please speak with a recruiter for additional information. Zone A: $163,600 — $225,000 USD Zone B: $155,400 — $213,700 USD Zone C: $147,300 — $202,500 USD Zone D: $139,000 — $191,200 USD Application Guidelines Candidates may submit up to 9 active applications within a 60-day period. Reapplications to the same role are accepted 90 days after a previous application has been reviewed. Use of AI in Our Hiring Process We may use automated AI tools to evaluate job applications for efficiency and consistency. These tools comply with local regulations, including bias audits, and we handle all personal data in accordance with state and local privacy laws. Contact us here with hiring practice or data usage questions. Every benefit we offer is designed with one goal: empowering you to do the best work of your career while building the life you want. Remote work, medical insurance, flexible time off, retirement savings plans, and modern family planning are just some of our offering. Check out our other benefits at Block. Block, Inc. (NYSE: XYZ) builds technology to increase access to the global economy. Each of our brands unlocks different aspects of the economy for more people. Square makes commerce and financial services accessible to sellers. Cash App is the easy way to spend, send, and store money. Afterpay is transforming the way customers manage their spending over time. TIDAL is a music platform that empowers artists to thrive as entrepreneurs. Bitkey is a simple self-custody wallet built for bitcoin. Proto is a suite of bitcoin mining products and services. Together, we’re helping build a financial system that is open to everyone. Privacy Policy</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>ET</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
         <v>100101001001.01</v>
       </c>
     </row>
